--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118622957</v>
+        <v>118622904</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565246</v>
+        <v>565230</v>
       </c>
       <c r="R2" t="n">
-        <v>7060733</v>
+        <v>7060695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622904</v>
+        <v>118622636</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565230</v>
+        <v>565131</v>
       </c>
       <c r="R4" t="n">
-        <v>7060695</v>
+        <v>7060772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118622822</v>
+        <v>118622539</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565231</v>
+        <v>565133</v>
       </c>
       <c r="R5" t="n">
-        <v>7060698</v>
+        <v>7060832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118622280</v>
+        <v>118622822</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565033</v>
+        <v>565231</v>
       </c>
       <c r="R6" t="n">
-        <v>7060844</v>
+        <v>7060698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118622539</v>
+        <v>118623077</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1300,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565133</v>
+        <v>565381</v>
       </c>
       <c r="R7" t="n">
-        <v>7060832</v>
+        <v>7060779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118622726</v>
+        <v>118622455</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1408,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1417,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565189</v>
+        <v>565107</v>
       </c>
       <c r="R8" t="n">
-        <v>7060731</v>
+        <v>7060840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118623069</v>
+        <v>118622280</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1525,7 +1520,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565369</v>
+        <v>565033</v>
       </c>
       <c r="R9" t="n">
-        <v>7060783</v>
+        <v>7060844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118622636</v>
+        <v>118622957</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565131</v>
+        <v>565246</v>
       </c>
       <c r="R10" t="n">
-        <v>7060772</v>
+        <v>7060733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118622938</v>
+        <v>118623069</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1754,7 +1754,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565237</v>
+        <v>565369</v>
       </c>
       <c r="R11" t="n">
-        <v>7060716</v>
+        <v>7060783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118623077</v>
+        <v>118622726</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1871,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565381</v>
+        <v>565189</v>
       </c>
       <c r="R12" t="n">
-        <v>7060779</v>
+        <v>7060731</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118622455</v>
+        <v>118622938</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565107</v>
+        <v>565237</v>
       </c>
       <c r="R13" t="n">
-        <v>7060840</v>
+        <v>7060716</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118622365</v>
+        <v>118622852</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565065</v>
+        <v>565231</v>
       </c>
       <c r="R3" t="n">
-        <v>7060836</v>
+        <v>7060698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622636</v>
+        <v>118622938</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565131</v>
+        <v>565237</v>
       </c>
       <c r="R4" t="n">
-        <v>7060772</v>
+        <v>7060716</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118622539</v>
+        <v>118622280</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1061,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565133</v>
+        <v>565033</v>
       </c>
       <c r="R5" t="n">
-        <v>7060832</v>
+        <v>7060844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118622822</v>
+        <v>118622726</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1169,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565231</v>
+        <v>565189</v>
       </c>
       <c r="R6" t="n">
-        <v>7060698</v>
+        <v>7060731</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118623077</v>
+        <v>118622636</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565381</v>
+        <v>565131</v>
       </c>
       <c r="R7" t="n">
-        <v>7060779</v>
+        <v>7060772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118622455</v>
+        <v>118622365</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565107</v>
+        <v>565065</v>
       </c>
       <c r="R8" t="n">
-        <v>7060840</v>
+        <v>7060836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118622280</v>
+        <v>118622539</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565033</v>
+        <v>565133</v>
       </c>
       <c r="R9" t="n">
-        <v>7060844</v>
+        <v>7060832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118622957</v>
+        <v>118623077</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565246</v>
+        <v>565381</v>
       </c>
       <c r="R10" t="n">
-        <v>7060733</v>
+        <v>7060779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118622726</v>
+        <v>118622957</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1871,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565189</v>
+        <v>565246</v>
       </c>
       <c r="R12" t="n">
-        <v>7060731</v>
+        <v>7060733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118622938</v>
+        <v>118622455</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565237</v>
+        <v>565107</v>
       </c>
       <c r="R13" t="n">
-        <v>7060716</v>
+        <v>7060840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118622904</v>
+        <v>118622726</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565230</v>
+        <v>565189</v>
       </c>
       <c r="R2" t="n">
-        <v>7060695</v>
+        <v>7060731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118622852</v>
+        <v>118622636</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565231</v>
+        <v>565131</v>
       </c>
       <c r="R3" t="n">
-        <v>7060698</v>
+        <v>7060772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622938</v>
+        <v>118622365</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565237</v>
+        <v>565065</v>
       </c>
       <c r="R4" t="n">
-        <v>7060716</v>
+        <v>7060836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118622280</v>
+        <v>118622822</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1071,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565033</v>
+        <v>565231</v>
       </c>
       <c r="R5" t="n">
-        <v>7060844</v>
+        <v>7060698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118622726</v>
+        <v>118623077</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1179,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565189</v>
+        <v>565381</v>
       </c>
       <c r="R6" t="n">
-        <v>7060731</v>
+        <v>7060779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118622636</v>
+        <v>118622904</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565131</v>
+        <v>565230</v>
       </c>
       <c r="R7" t="n">
-        <v>7060772</v>
+        <v>7060695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118622365</v>
+        <v>118622957</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565065</v>
+        <v>565246</v>
       </c>
       <c r="R8" t="n">
-        <v>7060836</v>
+        <v>7060733</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118622539</v>
+        <v>118622280</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565133</v>
+        <v>565033</v>
       </c>
       <c r="R9" t="n">
-        <v>7060832</v>
+        <v>7060844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118623077</v>
+        <v>118622455</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565381</v>
+        <v>565107</v>
       </c>
       <c r="R10" t="n">
-        <v>7060779</v>
+        <v>7060840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118623069</v>
+        <v>118622938</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1754,7 +1754,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565369</v>
+        <v>565237</v>
       </c>
       <c r="R11" t="n">
-        <v>7060783</v>
+        <v>7060716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118622957</v>
+        <v>118622539</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565246</v>
+        <v>565133</v>
       </c>
       <c r="R12" t="n">
-        <v>7060733</v>
+        <v>7060832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118622455</v>
+        <v>118623069</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1988,7 +1988,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565107</v>
+        <v>565369</v>
       </c>
       <c r="R13" t="n">
-        <v>7060840</v>
+        <v>7060783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118622726</v>
+        <v>118622957</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565189</v>
+        <v>565246</v>
       </c>
       <c r="R2" t="n">
-        <v>7060731</v>
+        <v>7060733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118622636</v>
+        <v>118622365</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565131</v>
+        <v>565065</v>
       </c>
       <c r="R3" t="n">
-        <v>7060772</v>
+        <v>7060836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622365</v>
+        <v>118622822</v>
       </c>
       <c r="B4" t="n">
-        <v>79572</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565065</v>
+        <v>565231</v>
       </c>
       <c r="R4" t="n">
-        <v>7060836</v>
+        <v>7060698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118622822</v>
+        <v>118622280</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565231</v>
+        <v>565033</v>
       </c>
       <c r="R5" t="n">
-        <v>7060698</v>
+        <v>7060844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118623077</v>
+        <v>118622938</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565381</v>
+        <v>565237</v>
       </c>
       <c r="R6" t="n">
-        <v>7060779</v>
+        <v>7060716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118622904</v>
+        <v>118622726</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1286,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565230</v>
+        <v>565189</v>
       </c>
       <c r="R7" t="n">
-        <v>7060695</v>
+        <v>7060731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118622957</v>
+        <v>118622539</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1412,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565246</v>
+        <v>565133</v>
       </c>
       <c r="R8" t="n">
-        <v>7060733</v>
+        <v>7060832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118622280</v>
+        <v>118622904</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1529,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565033</v>
+        <v>565230</v>
       </c>
       <c r="R9" t="n">
-        <v>7060844</v>
+        <v>7060695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118622455</v>
+        <v>118623077</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1646,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565107</v>
+        <v>565381</v>
       </c>
       <c r="R10" t="n">
-        <v>7060840</v>
+        <v>7060779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1723,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118622938</v>
+        <v>118622455</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565237</v>
+        <v>565107</v>
       </c>
       <c r="R11" t="n">
-        <v>7060716</v>
+        <v>7060840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118622539</v>
+        <v>118623069</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1871,7 +1876,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565133</v>
+        <v>565369</v>
       </c>
       <c r="R12" t="n">
-        <v>7060832</v>
+        <v>7060783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118623069</v>
+        <v>118622636</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,39 +1973,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565369</v>
+        <v>565131</v>
       </c>
       <c r="R13" t="n">
-        <v>7060783</v>
+        <v>7060772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118622822</v>
+        <v>119207336</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565231</v>
+        <v>565108</v>
       </c>
       <c r="R2" t="n">
-        <v>7060698</v>
+        <v>7060815</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118622636</v>
+        <v>119208645</v>
       </c>
       <c r="B3" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565131</v>
+        <v>565251</v>
       </c>
       <c r="R3" t="n">
-        <v>7060772</v>
+        <v>7060815</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622280</v>
+        <v>119208899</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,42 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565033</v>
+        <v>565228</v>
       </c>
       <c r="R4" t="n">
-        <v>7060844</v>
+        <v>7060820</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,70 +984,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118623069</v>
+        <v>119219139</v>
       </c>
       <c r="B5" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565369</v>
+        <v>565160</v>
       </c>
       <c r="R5" t="n">
-        <v>7060783</v>
+        <v>7060860</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23:24</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>23:24</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,27 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118622726</v>
+        <v>119206298</v>
       </c>
       <c r="B6" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,42 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565189</v>
+        <v>565029</v>
       </c>
       <c r="R6" t="n">
-        <v>7060731</v>
+        <v>7060828</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,27 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118622539</v>
+        <v>119206614</v>
       </c>
       <c r="B7" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565133</v>
+        <v>565026</v>
       </c>
       <c r="R7" t="n">
-        <v>7060832</v>
+        <v>7060836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,22 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,27 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118622938</v>
+        <v>119207160</v>
       </c>
       <c r="B8" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,42 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565237</v>
+        <v>565068</v>
       </c>
       <c r="R8" t="n">
-        <v>7060716</v>
+        <v>7060847</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,27 +1402,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118622904</v>
+        <v>119207604</v>
       </c>
       <c r="B9" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,42 +1425,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565230</v>
+        <v>565134</v>
       </c>
       <c r="R9" t="n">
-        <v>7060695</v>
+        <v>7060809</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1479,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,67 +1509,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118622957</v>
+        <v>118622636</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565246</v>
+        <v>565131</v>
       </c>
       <c r="R10" t="n">
-        <v>7060733</v>
+        <v>7060772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,55 +1628,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118623077</v>
+        <v>118622791</v>
       </c>
       <c r="B11" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565381</v>
+        <v>565178</v>
       </c>
       <c r="R11" t="n">
-        <v>7060779</v>
+        <v>7060680</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,58 +1735,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118622455</v>
+        <v>119207417</v>
       </c>
       <c r="B12" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565107</v>
+        <v>565093</v>
       </c>
       <c r="R12" t="n">
-        <v>7060840</v>
+        <v>7060841</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,22 +1800,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,65 +1830,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118622365</v>
+        <v>119207747</v>
       </c>
       <c r="B13" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565065</v>
+        <v>565169</v>
       </c>
       <c r="R13" t="n">
-        <v>7060836</v>
+        <v>7060798</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,22 +1907,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,65 +1937,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119207192</v>
+        <v>119208023</v>
       </c>
       <c r="B14" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565071</v>
+        <v>565193</v>
       </c>
       <c r="R14" t="n">
-        <v>7060842</v>
+        <v>7060819</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2144,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,65 +2044,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119208899</v>
+        <v>119219140</v>
       </c>
       <c r="B15" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565228</v>
+        <v>565185</v>
       </c>
       <c r="R15" t="n">
-        <v>7060820</v>
+        <v>7060883</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,19 +2124,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,15 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119208746</v>
+        <v>119206359</v>
       </c>
       <c r="B16" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565223</v>
+        <v>565010</v>
       </c>
       <c r="R16" t="n">
-        <v>7060817</v>
+        <v>7060855</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2379,11 +2234,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,53 +2260,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119206298</v>
+        <v>118622365</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565029</v>
+        <v>565065</v>
       </c>
       <c r="R17" t="n">
-        <v>7060828</v>
+        <v>7060836</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,22 +2325,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,27 +2355,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119208095</v>
+        <v>119207192</v>
       </c>
       <c r="B18" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,37 +2378,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565200</v>
+        <v>565071</v>
       </c>
       <c r="R18" t="n">
-        <v>7060802</v>
+        <v>7060842</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2608,11 +2448,6 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,53 +2474,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119208147</v>
+        <v>119207278</v>
       </c>
       <c r="B19" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565200</v>
+        <v>565112</v>
       </c>
       <c r="R19" t="n">
-        <v>7060802</v>
+        <v>7060822</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2751,15 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119208392</v>
+        <v>119207547</v>
       </c>
       <c r="B20" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,37 +2592,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565231</v>
+        <v>565117</v>
       </c>
       <c r="R20" t="n">
-        <v>7060739</v>
+        <v>7060821</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2826,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,12 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,27 +2676,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119208645</v>
+        <v>119208162</v>
       </c>
       <c r="B21" t="n">
-        <v>80481</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,37 +2699,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565251</v>
+        <v>565174</v>
       </c>
       <c r="R21" t="n">
-        <v>7060815</v>
+        <v>7060775</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2980,53 +2795,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119208716</v>
+        <v>119219133</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565228</v>
+        <v>565032</v>
       </c>
       <c r="R22" t="n">
-        <v>7060804</v>
+        <v>7060882</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,24 +2863,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,53 +2892,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119208050</v>
+        <v>119208157</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565199</v>
+        <v>565172</v>
       </c>
       <c r="R23" t="n">
-        <v>7060828</v>
+        <v>7060782</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3183,11 +2973,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,50 +2999,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119208162</v>
+        <v>119208147</v>
       </c>
       <c r="B24" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565174</v>
+        <v>565200</v>
       </c>
       <c r="R24" t="n">
-        <v>7060775</v>
+        <v>7060802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3326,15 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119207986</v>
+        <v>118622280</v>
       </c>
       <c r="B25" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,17 +3142,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565212</v>
+        <v>565033</v>
       </c>
       <c r="R25" t="n">
         <v>7060844</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3401,27 +3176,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,27 +3206,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119207834</v>
+        <v>118622455</v>
       </c>
       <c r="B26" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3489,17 +3254,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565165</v>
+        <v>565107</v>
       </c>
       <c r="R26" t="n">
-        <v>7060869</v>
+        <v>7060840</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3523,27 +3288,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,27 +3318,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119207547</v>
+        <v>118622539</v>
       </c>
       <c r="B27" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3586,37 +3341,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565117</v>
+        <v>565133</v>
       </c>
       <c r="R27" t="n">
-        <v>7060821</v>
+        <v>7060832</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,22 +3400,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,62 +3430,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119206614</v>
+        <v>118622726</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565026</v>
+        <v>565189</v>
       </c>
       <c r="R28" t="n">
-        <v>7060836</v>
+        <v>7060731</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,22 +3512,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,62 +3542,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119208157</v>
+        <v>118622822</v>
       </c>
       <c r="B29" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565172</v>
+        <v>565231</v>
       </c>
       <c r="R29" t="n">
-        <v>7060782</v>
+        <v>7060698</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,22 +3624,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,44 +3654,39 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119207927</v>
+        <v>118622904</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3940,19 +3695,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565183</v>
+        <v>565230</v>
       </c>
       <c r="R30" t="n">
-        <v>7060849</v>
+        <v>7060695</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3976,22 +3736,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,27 +3766,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119206359</v>
+        <v>118622938</v>
       </c>
       <c r="B31" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,37 +3789,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565010</v>
+        <v>565237</v>
       </c>
       <c r="R31" t="n">
-        <v>7060855</v>
+        <v>7060716</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4088,22 +3848,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,65 +3878,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119207160</v>
+        <v>118622957</v>
       </c>
       <c r="B32" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565068</v>
+        <v>565246</v>
       </c>
       <c r="R32" t="n">
-        <v>7060847</v>
+        <v>7060733</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4200,22 +3960,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4230,65 +3990,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119207604</v>
+        <v>118623069</v>
       </c>
       <c r="B33" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565134</v>
+        <v>565369</v>
       </c>
       <c r="R33" t="n">
-        <v>7060809</v>
+        <v>7060783</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4312,22 +4072,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4342,27 +4102,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119207807</v>
+        <v>118623077</v>
       </c>
       <c r="B34" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4395,17 +4150,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565146</v>
+        <v>565381</v>
       </c>
       <c r="R34" t="n">
-        <v>7060858</v>
+        <v>7060779</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4429,27 +4184,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,27 +4214,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119208023</v>
+        <v>119206274</v>
       </c>
       <c r="B35" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,34 +4237,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565193</v>
+        <v>565021</v>
       </c>
       <c r="R35" t="n">
-        <v>7060819</v>
+        <v>7060852</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4551,7 +4296,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4561,7 +4306,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4576,27 +4326,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119207417</v>
+        <v>119207462</v>
       </c>
       <c r="B36" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,34 +4349,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565093</v>
+        <v>565106</v>
       </c>
       <c r="R36" t="n">
-        <v>7060841</v>
+        <v>7060802</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4674,6 +4419,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4700,15 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119207278</v>
+        <v>119207807</v>
       </c>
       <c r="B37" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,34 +4461,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565112</v>
+        <v>565146</v>
       </c>
       <c r="R37" t="n">
-        <v>7060822</v>
+        <v>7060858</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4775,7 +4525,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4785,7 +4535,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4800,27 +4555,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119206274</v>
+        <v>119207834</v>
       </c>
       <c r="B38" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4846,16 +4596,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565021</v>
+        <v>565165</v>
       </c>
       <c r="R38" t="n">
-        <v>7060852</v>
+        <v>7060869</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4887,7 +4642,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4897,12 +4652,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4917,27 +4672,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119207747</v>
+        <v>119207986</v>
       </c>
       <c r="B39" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4945,34 +4695,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565169</v>
+        <v>565212</v>
       </c>
       <c r="R39" t="n">
-        <v>7060798</v>
+        <v>7060844</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5004,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5014,7 +4769,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5041,15 +4801,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119206732</v>
+        <v>119208050</v>
       </c>
       <c r="B40" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5057,42 +4812,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565022</v>
+        <v>565199</v>
       </c>
       <c r="R40" t="n">
-        <v>7060838</v>
+        <v>7060828</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5132,6 +4882,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5158,15 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119208665</v>
+        <v>119208095</v>
       </c>
       <c r="B41" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5174,34 +4924,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565248</v>
+        <v>565200</v>
       </c>
       <c r="R41" t="n">
-        <v>7060815</v>
+        <v>7060802</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5244,6 +4994,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5270,15 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119219140</v>
+        <v>119208392</v>
       </c>
       <c r="B42" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5286,37 +5036,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565185</v>
+        <v>565231</v>
       </c>
       <c r="R42" t="n">
-        <v>7060883</v>
+        <v>7060739</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5343,9 +5093,24 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5372,53 +5137,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119219139</v>
+        <v>119208716</v>
       </c>
       <c r="B43" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565160</v>
+        <v>565228</v>
       </c>
       <c r="R43" t="n">
-        <v>7060860</v>
+        <v>7060804</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5445,9 +5205,24 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5471,6 +5246,556 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>119208746</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>565223</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7060817</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119206732</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>565022</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7060838</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>119207927</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>565183</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7060849</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Hillevi Nydahl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Hillevi Nydahl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>119205875</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>565002</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7060872</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>119208665</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>565248</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7060815</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27635-2024 artfynd.xlsx
+++ b/artfynd/A 27635-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219139</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119206298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119206614</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207604</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622636</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207417</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207747</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208023</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219140</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119206359</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622365</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207192</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207278</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207547</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208162</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219133</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208157</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3103,6 +3218,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208147</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3215,6 +3335,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622280</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3327,6 +3452,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622455</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3439,6 +3569,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622539</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622726</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3663,6 +3803,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622822</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622904</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3887,6 +4037,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622938</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3999,6 +4154,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622957</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4111,6 +4271,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118623069</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4223,6 +4388,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118623077</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4335,6 +4505,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119206274</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4447,6 +4622,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207462</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4564,6 +4744,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207807</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4681,6 +4866,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207834</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4798,6 +4988,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207986</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4910,6 +5105,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208050</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5022,6 +5222,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208095</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5134,6 +5339,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208392</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5246,6 +5456,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208716</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5358,6 +5573,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208746</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5470,6 +5690,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119206732</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5577,6 +5802,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119207927</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5689,6 +5919,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119205875</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5796,8 +6031,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>